--- a/dataset/construct/dataset_splits/data_size/20_percent/tum/fold3.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/tum/fold3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>662</v>
+        <v>344</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,123 +625,114 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82.8652711232793</v>
+        <v>85.91221886328491</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>25.8805706350208</v>
       </c>
       <c r="E2" t="n">
-        <v>26.0422405876951</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>432</v>
       </c>
       <c r="I2" t="n">
-        <v>10800</v>
+        <v>378</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="K2" t="n">
-        <v>169</v>
+        <v>1013</v>
       </c>
       <c r="L2" t="n">
-        <v>515</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="N2" t="n">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X2" t="n">
-        <v>25.1</v>
+        <v>28.6082260699118</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.154411764705882</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.4647313470843</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>25.0500676016111</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>184</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.1056030876873</v>
+        <v>77.5943455776105</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>34.2058298631766</v>
       </c>
       <c r="E3" t="n">
-        <v>25.390625</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>376.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5640</v>
+        <v>275.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>276.5</v>
       </c>
       <c r="K3" t="n">
-        <v>282</v>
+        <v>928.5</v>
       </c>
       <c r="L3" t="n">
-        <v>283</v>
+        <v>25.6</v>
       </c>
       <c r="M3" t="n">
-        <v>266</v>
+        <v>33.7</v>
       </c>
       <c r="N3" t="n">
-        <v>831</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>158</v>
+        <v>123.9</v>
       </c>
       <c r="P3" t="n">
-        <v>41</v>
+        <v>22.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>22.9</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>0.19</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>24.859943977591</v>
       </c>
       <c r="X3" t="n">
-        <v>24.4</v>
+        <v>24.5496573149696</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.281690140845071</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.8260951566085</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -845,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -863,24 +839,13 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>146</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1962</v>
+        <v>2013</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -888,79 +853,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.1123504322255</v>
+        <v>92.0309740284432</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>26.7949380165289</v>
       </c>
       <c r="E4" t="n">
-        <v>25.0593070266296</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>262.3</v>
       </c>
       <c r="I4" t="n">
-        <v>35000</v>
+        <v>377.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="K4" t="n">
-        <v>783.1</v>
+        <v>919.7</v>
       </c>
       <c r="L4" t="n">
-        <v>744.9</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1697</v>
+        <v>29.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4</v>
+        <v>36.7</v>
       </c>
       <c r="P4" t="n">
-        <v>196.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>196.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>92.3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="V4" t="n">
-        <v>92.3</v>
+        <v>0.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X4" t="n">
-        <v>28.15</v>
+        <v>26.4561900936673</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.19551282051282</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>28.5841609371021</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.1846427181971</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -981,30 +946,19 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>156</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>336</v>
+        <v>1025</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1012,80 +966,82 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.0155395213831</v>
+        <v>85.2467825500038</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>30.3460743801652</v>
       </c>
       <c r="E5" t="n">
-        <v>19.7231833910034</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>242.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>371.3</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>285.3</v>
       </c>
       <c r="K5" t="n">
-        <v>652</v>
+        <v>899.4000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>918</v>
+        <v>72.3</v>
       </c>
       <c r="M5" t="n">
-        <v>547</v>
+        <v>106.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2117</v>
+        <v>85.3</v>
       </c>
       <c r="O5" t="n">
-        <v>95</v>
+        <v>264.3</v>
       </c>
       <c r="P5" t="n">
-        <v>157</v>
+        <v>22.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>344</v>
+        <v>53.2</v>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>75.80000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>88</v>
+        <v>26.9</v>
       </c>
       <c r="V5" t="n">
-        <v>142</v>
+        <v>0.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>27.1836007130125</v>
       </c>
       <c r="X5" t="n">
-        <v>26.4</v>
+        <v>26.8217134966894</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.204081632653061</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.0562770562771</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.6741965227618</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1094,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1109,24 +1065,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>186</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2006</v>
+        <v>2319</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1134,85 +1079,85 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.10314342662311</v>
+        <v>77.2493207024615</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.515625</v>
       </c>
       <c r="E6" t="n">
-        <v>33.8123415046491</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>55.8</v>
       </c>
       <c r="I6" t="n">
-        <v>391</v>
+        <v>46.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>14.9</v>
       </c>
       <c r="K6" t="n">
-        <v>718.6</v>
+        <v>117.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1023.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2277.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>140.7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>59.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>252.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>100.6</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>105.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X6" t="n">
-        <v>27.2</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0912280701754387</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.6610644257703</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.3480481672903</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1221,36 +1166,27 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1258,85 +1194,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.0683245874211</v>
+        <v>74.1720111795574</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.9515570934256</v>
       </c>
       <c r="E7" t="n">
-        <v>21.484375</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="I7" t="n">
-        <v>882</v>
+        <v>215</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="K7" t="n">
-        <v>153</v>
+        <v>557</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
+        <v>68</v>
+      </c>
+      <c r="P7" t="n">
         <v>49</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>49</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X7" t="n">
-        <v>19.8</v>
+        <v>22.3940969210825</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.255506607929515</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.690094219506</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1186577456453</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1345,36 +1281,27 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>696</v>
+        <v>2093</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1382,85 +1309,85 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>78.7061113329277</v>
+        <v>84.1487284521003</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>29.0174471992653</v>
       </c>
       <c r="E8" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>489.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4960</v>
+        <v>405.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>217.9</v>
       </c>
       <c r="K8" t="n">
-        <v>842.5</v>
+        <v>1113</v>
       </c>
       <c r="L8" t="n">
-        <v>476.1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>627.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1946.2</v>
+        <v>15.1</v>
       </c>
       <c r="O8" t="n">
-        <v>110.9</v>
+        <v>15.1</v>
       </c>
       <c r="P8" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>219.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>409.9</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>57.7</v>
+        <v>23.95</v>
       </c>
       <c r="V8" t="n">
-        <v>97.09999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>23.9686783804431</v>
       </c>
       <c r="X8" t="n">
-        <v>24.3</v>
+        <v>22.9720679092787</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.206642066420664</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.2551566080978</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.9911309690755</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1469,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1481,24 +1408,15 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>166</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>323</v>
+        <v>546</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1506,83 +1424,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>79.7188668339798</v>
+        <v>83.8833922731767</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>33.0904223676383</v>
       </c>
       <c r="E9" t="n">
-        <v>28.0403781445281</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="K9" t="n">
-        <v>209</v>
+        <v>422</v>
       </c>
       <c r="L9" t="n">
-        <v>137.7</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>431.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>50</v>
+        <v>22.1</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
+        <v>0.39</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>22.9182582123759</v>
       </c>
       <c r="X9" t="n">
-        <v>22.1</v>
+        <v>21.7452723622298</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.350746268656717</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.406057760656</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1594,33 +1514,22 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>103</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>140</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1205</v>
+        <v>551</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1628,123 +1537,114 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.3262297196238</v>
+        <v>86.878606738155</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>23.1481481481481</v>
       </c>
       <c r="E10" t="n">
-        <v>21.09375</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>852</v>
       </c>
       <c r="I10" t="n">
-        <v>1550</v>
+        <v>377</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>892</v>
       </c>
       <c r="K10" t="n">
-        <v>242</v>
+        <v>2121</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>308</v>
+        <v>204</v>
       </c>
       <c r="O10" t="n">
-        <v>37</v>
+        <v>552</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X10" t="n">
-        <v>20.8</v>
+        <v>23.5033791921504</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.15929203539823</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8945249963572</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>299</v>
+        <v>600</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1752,77 +1652,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.3335159517834</v>
+        <v>87.4373393413948</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>24.4444444444444</v>
       </c>
       <c r="E11" t="n">
-        <v>28.4567901234567</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>480</v>
+      </c>
+      <c r="I11" t="n">
+        <v>127</v>
+      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="K11" t="n">
-        <v>455</v>
+        <v>741</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>200</v>
       </c>
       <c r="M11" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>629</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V11" t="n">
-        <v>86</v>
+        <v>0.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>20.2762923351159</v>
       </c>
       <c r="X11" t="n">
-        <v>26.3</v>
+        <v>19.9151768367782</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.258278145695364</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.8406888888731</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1843,25 +1745,16 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
